--- a/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E2" t="n">
-        <v>1544</v>
+        <v>1877</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2788887100714704</v>
+        <v>0.2274601493467305</v>
       </c>
       <c r="H2" t="n">
-        <v>597.139684767698</v>
+        <v>552.6481254821807</v>
       </c>
       <c r="I2" t="n">
-        <v>9.159653958517076e-112</v>
+        <v>2.509992414891764e-107</v>
       </c>
       <c r="J2" t="n">
-        <v>172.1361681705525</v>
+        <v>210.6653267677102</v>
       </c>
       <c r="K2" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L2" t="n">
-        <v>66.5734049212974</v>
+        <v>62.02653060323181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.111487155550876</v>
+        <v>0.1122351234777358</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7216232857673603, 'N1ratio-ArgsPreds': -0.20623521687888982}</t>
+          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.823844912460471e-164, 'N1ratio-ArgsPreds': 9.159653958519536e-112}</t>
+          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5280991479556377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.888871007146914)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -628,80 +628,80 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E3" t="n">
-        <v>1541</v>
+        <v>1876</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3351199849338026</v>
+        <v>0.2613785615094218</v>
       </c>
       <c r="H3" t="n">
-        <v>194.1778535528601</v>
+        <v>331.9333530270461</v>
       </c>
       <c r="I3" t="n">
-        <v>6.876195971999602e-135</v>
+        <v>3.799710820148012e-124</v>
       </c>
       <c r="J3" t="n">
-        <v>158.7132245537547</v>
+        <v>201.4160519559927</v>
       </c>
       <c r="K3" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L3" t="n">
-        <v>19.9990871345238</v>
+        <v>35.63790270747462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1029936564268363</v>
+        <v>0.1073646332388021</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5920993353367638, 'N1ratio-ArgsPreds': -0.21008109385060292, 'latitude': 0.003788815465326568, 'longitude': -4.566087073707778e-06, 'Macro_class': 0.0451128018370466}</t>
+          <t>{'const': 0.48189262791408727, 'N1ratio-ArgsPreds': -2.228335490076547, 'Macro_class': 0.03889919108171541}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.1460070432133304e-100, 'N1ratio-ArgsPreds': 2.7241569733103175e-112, 'latitude': 2.0105321689319718e-14, 'longitude': 0.9648727161654734, 'Macro_class': 1.810321629638847e-21}</t>
+          <t>{'const': 1.5067923387317399e-108, 'N1ratio-ArgsPreds': 2.1928357561400054e-112, 'Macro_class': 4.4572314883263724e-20}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5379471476457032, 'latitude': 0.16892586870392384, 'longitude': -0.0009843143319924143, 'Macro_class': 0.2056838925374642}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4791296318773468, 'Macro_class': 0.1841826813802799}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5296028099294897), 'latitude': np.float64(0.193070598681436), 'longitude': np.float64(-0.0011220543053802913), 'Macro_class': np.float64(0.23891601510265767)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48691125219185455), 'Macro_class': np.float64(0.20953535440864834)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5090966326675047), 'latitude': np.float64(0.16044897288356422), 'longitude': np.float64(-0.0009149256209509112), 'Macro_class': np.float64(0.20062251798959566)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4790953945547619), 'Macro_class': np.float64(0.18416952017826255)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(25.917938139339224), 'latitude': np.float64(2.5743872899390725), 'longitude': np.float64(8.370888918724104e-05), 'Macro_class': np.float64(4.024939472448564)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.9532397083583), 'Macro_class': np.float64(3.391841216269145)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.05623127486233215</v>
+        <v>0.03391841216269131</v>
       </c>
       <c r="V3" t="n">
-        <v>43.44262252802935</v>
+        <v>86.14824577423984</v>
       </c>
       <c r="W3" t="n">
-        <v>6.001493159104878e-27</v>
+        <v>4.457231488324809e-20</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E4" t="n">
-        <v>1540</v>
+        <v>1875</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3358954086663867</v>
+        <v>0.2619344462490172</v>
       </c>
       <c r="H4" t="n">
-        <v>155.7823680476198</v>
+        <v>221.8082500580562</v>
       </c>
       <c r="I4" t="n">
-        <v>4.170842569285563e-134</v>
+        <v>3.866913495938532e-123</v>
       </c>
       <c r="J4" t="n">
-        <v>158.5281234855843</v>
+        <v>201.2644667138683</v>
       </c>
       <c r="K4" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L4" t="n">
-        <v>16.03628992125313</v>
+        <v>23.80913021902455</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1029403399257041</v>
+        <v>0.1073410489140631</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5986196932832282, 'N1ratio-ArgsPreds': -0.20686377387951788, 'latitude': 0.0038003308375348654, 'longitude': -4.031102623384531e-05, 'Macro_class': 0.046025152341286533, 'Fam_class': -0.00032243452209890574}</t>
+          <t>{'const': 0.488758508217601, 'N1ratio-ArgsPreds': -2.2046729341499987, 'Macro_class': 0.0393982582812695, 'Fam_class': -0.00022345939545314323}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.3719407742700062e-99, 'N1ratio-ArgsPreds': 1.0482111701943141e-102, 'latitude': 1.6734942419767786e-14, 'longitude': 0.7064475226020194, 'Macro_class': 7.538214510784381e-22, 'Fam_class': 0.18013535613409756}</t>
+          <t>{'const': 4.8767719986787777e-104, 'N1ratio-ArgsPreds': 4.2965559556711e-106, 'Macro_class': 2.3055494328102562e-20, 'Fam_class': 0.23484477702689188}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5297086713992897, 'latitude': 0.16943928622756352, 'longitude': -0.0086898738939457, 'Macro_class': 0.2098435943389268, 'Fam_class': -0.029619705700312356}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4740417841269281, 'Macro_class': 0.186545700570312, 'Fam_class': -0.024241333374891254}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5096588369434795), 'latitude': np.float64(0.19371561511617877), 'longitude': np.float64(-0.009598794712681876), 'Macro_class': np.float64(0.24120124994063472), 'Fam_class': np.float64(-0.034150565916667)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4746933756265527), 'Macro_class': np.float64(0.21116941052515278), 'Fam_class': np.float64(-0.02743351278883546)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4827354770349507), 'latitude': np.float64(0.16091195426469926), 'longitude': np.float64(-0.007822668978782919), 'Macro_class': np.float64(0.20254120521153235), 'Fam_class': np.float64(-0.027846431236075636)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46334377869449395), 'Macro_class': np.float64(0.18560264348520186), 'Fam_class': np.float64(-0.02357720805344872)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.303354078816138), 'latitude': np.float64(2.5892657025284667), 'longitude': np.float64(0.006119414995161259), 'Macro_class': np.float64(4.1022939808540055), 'Fam_class': np.float64(0.07754237325854889)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.468745725489217), 'Macro_class': np.float64(3.4448341268694946), 'Fam_class': np.float64(0.055588473959560715)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0007754237325841018</v>
+        <v>0.0005558847395953359</v>
       </c>
       <c r="V4" t="n">
-        <v>1.798139274690895</v>
+        <v>1.412183350712114</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1801353561342204</v>
+        <v>0.2348447770264812</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E5" t="n">
-        <v>1538</v>
+        <v>1873</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3450160878646346</v>
+        <v>0.2696056640049717</v>
       </c>
       <c r="H5" t="n">
-        <v>115.7356110594802</v>
+        <v>138.2736376216228</v>
       </c>
       <c r="I5" t="n">
-        <v>1.676257582139428e-136</v>
+        <v>5.057909186436417e-125</v>
       </c>
       <c r="J5" t="n">
-        <v>156.3509300478628</v>
+        <v>199.1725880957001</v>
       </c>
       <c r="K5" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L5" t="n">
-        <v>11.7655204348553</v>
+        <v>14.70385385504837</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1016586021117444</v>
+        <v>0.1063388083799787</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.6613995821693961, 'N1ratio-ArgsPreds': -0.20022658501321183, 'latitude': 0.003904782868167093, 'longitude': -0.00013919989562284846, 'Macro_class': 0.041249893628343776, 'Fam_class': -0.0005341528657763941, 'Nlen_freq': -0.05245277165013973, 'Vlen_freq': 0.04521620320763898}</t>
+          <t>{'const': 0.5046776201284493, 'N1ratio-ArgsPreds': -2.1556362407536405, 'Macro_class': 0.03353246780825911, 'Fam_class': -0.000375076565640423, 'Nlen_freq': -0.4222864235676891, 'Vlen_freq': 0.5326304691843448}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.4679513017458327e-38, 'N1ratio-ArgsPreds': 2.6913691577768e-95, 'latitude': 2.5250829575406025e-15, 'longitude': 0.20243259343697534, 'Macro_class': 3.541864495018582e-16, 'Fam_class': 0.029582124451356717, 'Nlen_freq': 1.099034877332113e-05, 'Vlen_freq': 1.0268744561068315e-05}</t>
+          <t>{'const': 4.707402591774876e-57, 'N1ratio-ArgsPreds': 2.6206041863877893e-101, 'Macro_class': 1.5464474263982936e-13, 'Fam_class': 0.05095891044160416, 'Nlen_freq': 0.00010126742949760403, 'Vlen_freq': 1.0795693038448011e-05}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5127130591165668, 'latitude': 0.1740963222257306, 'longitude': -0.030007411173207665, 'Macro_class': 0.18807164136869625, 'Fam_class': -0.04906872434218462, 'Nlen_freq': -0.16839277217585, 'Vlen_freq': 0.17778809172835128}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4634980697894284, 'Macro_class': 0.15877193490345254, 'Fam_class': -0.040689074855683724, 'Nlen_freq': -0.1405620037501508, 'Vlen_freq': 0.1688113034162253}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4934305412228254), 'latitude': np.float64(0.19975306738554952), 'longitude': np.float64(-0.032498939063819676), 'Macro_class': np.float64(0.20570605550116072), 'Fam_class': np.float64(-0.055442836886884554), 'Nlen_freq': np.float64(-0.1117780702482574), 'Vlen_freq': np.float64(0.11215005622049709)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46518437150522135), 'Macro_class': np.float64(0.16938491657459173), 'Fam_class': np.float64(-0.045082628434283095), 'Nlen_freq': np.float64(-0.08965770840684999), 'Vlen_freq': np.float64(0.1014327148711638)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4591232942458281), 'latitude': np.float64(0.1649874194744548), 'longitude': np.float64(-0.026315641903484864), 'Macro_class': np.float64(0.17011830467528202), 'Fam_class': np.float64(-0.04493960793348434), 'Nlen_freq': np.float64(-0.09103368573944236), 'Vlen_freq': np.float64(0.09134048898367954)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.449113004068729), 'Macro_class': np.float64(0.14688409858336846), 'Fam_class': np.float64(-0.03856823063612457), 'Nlen_freq': np.float64(-0.07693410846833972), 'Vlen_freq': np.float64(0.08713697129752625)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.079419931914124), 'latitude': np.float64(2.722084858483971), 'longitude': np.float64(0.06925130087924485), 'Macro_class': np.float64(2.894023758559208), 'Fam_class': np.float64(0.20195683612152884), 'Nlen_freq': np.float64(0.8287131939307552), 'Vlen_freq': np.float64(0.8343084927777683)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.17024904236382), 'Macro_class': np.float64(2.1574938416648703), 'Fam_class': np.float64(0.1487508414401298), 'Nlen_freq': np.float64(0.5918857045818261), 'Vlen_freq': np.float64(0.7592851766905914)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.009120679198247883</v>
+        <v>0.007671217755954474</v>
       </c>
       <c r="V5" t="n">
-        <v>10.7083581344561</v>
+        <v>9.835913388709884</v>
       </c>
       <c r="W5" t="n">
-        <v>2.407140461331682e-05</v>
+        <v>5.631105420961853e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2274601493467305</v>
+        <v>0.2216711997682284</v>
       </c>
       <c r="H2" t="n">
-        <v>552.6481254821807</v>
+        <v>534.5772144639448</v>
       </c>
       <c r="I2" t="n">
-        <v>2.509992414891764e-107</v>
+        <v>2.805806715175607e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.6653267677102</v>
+        <v>210.7278626313512</v>
       </c>
       <c r="K2" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>62.02653060323181</v>
+        <v>60.01615014140037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122351234777358</v>
+        <v>0.1122684404002936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
+          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
+          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2613785615094218</v>
+        <v>0.2561305929104448</v>
       </c>
       <c r="H3" t="n">
-        <v>331.9333530270461</v>
+        <v>322.9740245535776</v>
       </c>
       <c r="I3" t="n">
-        <v>3.799710820148012e-124</v>
+        <v>2.910065023966609e-121</v>
       </c>
       <c r="J3" t="n">
-        <v>201.4160519559927</v>
+        <v>201.3981882543137</v>
       </c>
       <c r="K3" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>35.63790270747462</v>
+        <v>34.67291225921895</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1073646332388021</v>
+        <v>0.1073551110097621</v>
       </c>
       <c r="N3" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.48189262791408727, 'N1ratio-ArgsPreds': -2.228335490076547, 'Macro_class': 0.03889919108171541}</t>
+          <t>{'const': 0.468074736893736, 'N1ratio-ArgsPreds': -2.1541524464711896, 'Macro_class': 0.03906670331136904}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.5067923387317399e-108, 'N1ratio-ArgsPreds': 2.1928357561400054e-112, 'Macro_class': 4.4572314883263724e-20}</t>
+          <t>{'const': 1.6529452894676226e-104, 'N1ratio-ArgsPreds': 4.686242165715662e-109, 'Macro_class': 3.092084722918587e-20}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4791296318773468, 'Macro_class': 0.1841826813802799}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4725017184539223, 'Macro_class': 0.18564003418732464}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48691125219185455), 'Macro_class': np.float64(0.20953535440864834)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48044962994406476), 'Macro_class': np.float64(0.21041285155911574)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4790953945547619), 'Macro_class': np.float64(0.18416952017826255)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4724823232149074), 'Macro_class': np.float64(0.18563241403972688)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.9532397083583), 'Macro_class': np.float64(3.391841216269145)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.323954575055623), 'Macro_class': np.float64(3.445939314221659)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.03391841216269131</v>
+        <v>0.03445939314221647</v>
       </c>
       <c r="V3" t="n">
-        <v>86.14824577423984</v>
+        <v>86.9047993084293</v>
       </c>
       <c r="W3" t="n">
-        <v>4.457231488324809e-20</v>
+        <v>3.092084722918151e-20</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2619344462490172</v>
+        <v>0.2568493439592349</v>
       </c>
       <c r="H4" t="n">
-        <v>221.8082500580562</v>
+        <v>216.0138575800651</v>
       </c>
       <c r="I4" t="n">
-        <v>3.866913495938532e-123</v>
+        <v>2.391569004212337e-120</v>
       </c>
       <c r="J4" t="n">
-        <v>201.2644667138683</v>
+        <v>201.2035907111796</v>
       </c>
       <c r="K4" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>23.80913021902455</v>
+        <v>23.18014068719065</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1073410489140631</v>
+        <v>0.1073085817126291</v>
       </c>
       <c r="N4" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.488758508217601, 'N1ratio-ArgsPreds': -2.2046729341499987, 'Macro_class': 0.0393982582812695, 'Fam_class': -0.00022345939545314323}</t>
+          <t>{'const': 0.4759888597113042, 'N1ratio-ArgsPreds': -2.128302572359495, 'Macro_class': 0.039635394293468545, 'Fam_class': -0.00025296341176478084}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 4.8767719986787777e-104, 'N1ratio-ArgsPreds': 4.2965559556711e-106, 'Macro_class': 2.3055494328102562e-20, 'Fam_class': 0.23484477702689188}</t>
+          <t>{'const': 2.6617230041474045e-100, 'N1ratio-ArgsPreds': 7.408631313802145e-103, 'Macro_class': 1.369513523252418e-20, 'Fam_class': 0.1782590179604581}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4740417841269281, 'Macro_class': 0.186545700570312, 'Fam_class': -0.024241333374891254}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46683168801591796, 'Macro_class': 0.18834238182381569, 'Fam_class': -0.027540527164735602}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4746933756265527), 'Macro_class': np.float64(0.21116941052515278), 'Fam_class': np.float64(-0.02743351278883546)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4681480710880722), 'Macro_class': np.float64(0.2124084751565065), 'Fam_class': np.float64(-0.031084286040385028)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46334377869449395), 'Macro_class': np.float64(0.18560264348520186), 'Fam_class': np.float64(-0.02357720805344872)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45671089532940834), 'Macro_class': np.float64(0.18738519505749102), 'Fam_class': np.float64(-0.02680953279693525)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.468745725489217), 'Macro_class': np.float64(3.4448341268694946), 'Fam_class': np.float64(0.055588473959560715)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.858484191258977), 'Macro_class': np.float64(3.511321132673396), 'Fam_class': np.float64(0.07187510487899469)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0005558847395953359</v>
+        <v>0.000718751048790045</v>
       </c>
       <c r="V4" t="n">
-        <v>1.412183350712114</v>
+        <v>1.8134387765479</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2348447770264812</v>
+        <v>0.1782590179603268</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2696056640049717</v>
+        <v>0.2657158657219123</v>
       </c>
       <c r="H5" t="n">
-        <v>138.2736376216228</v>
+        <v>135.556739758906</v>
       </c>
       <c r="I5" t="n">
-        <v>5.057909186436417e-125</v>
+        <v>7.158313357665104e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>199.1725880957001</v>
+        <v>198.8030330298154</v>
       </c>
       <c r="K5" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L5" t="n">
-        <v>14.70385385504837</v>
+        <v>14.38819594858723</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1063388083799787</v>
+        <v>0.1061415018845784</v>
       </c>
       <c r="N5" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.5046776201284493, 'N1ratio-ArgsPreds': -2.1556362407536405, 'Macro_class': 0.03353246780825911, 'Fam_class': -0.000375076565640423, 'Nlen_freq': -0.4222864235676891, 'Vlen_freq': 0.5326304691843448}</t>
+          <t>{'const': 0.4966621923199189, 'N1ratio-ArgsPreds': -2.079498707297034, 'Macro_class': 0.0335176877291935, 'Fam_class': -0.0004085471162188468, 'Nlen_freq': -0.45832254757103325, 'Vlen_freq': 0.5661226375859589}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 4.707402591774876e-57, 'N1ratio-ArgsPreds': 2.6206041863877893e-101, 'Macro_class': 1.5464474263982936e-13, 'Fam_class': 0.05095891044160416, 'Nlen_freq': 0.00010126742949760403, 'Vlen_freq': 1.0795693038448011e-05}</t>
+          <t>{'const': 1.2789872833284822e-55, 'N1ratio-ArgsPreds': 3.199367485890837e-98, 'Macro_class': 1.4609515341634866e-13, 'Fam_class': 0.033169445271857965, 'Nlen_freq': 2.2739211578145297e-05, 'Vlen_freq': 2.623427328964937e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4634980697894284, 'Macro_class': 0.15877193490345254, 'Fam_class': -0.040689074855683724, 'Nlen_freq': -0.1405620037501508, 'Vlen_freq': 0.1688113034162253}</t>
+          <t>{'N1ratio-ArgsPreds': -0.456126823489277, 'Macro_class': 0.15927181380868616, 'Fam_class': -0.044479171409823874, 'Nlen_freq': -0.15327235179880677, 'Vlen_freq': 0.1803240571907867}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46518437150522135), 'Macro_class': np.float64(0.16938491657459173), 'Fam_class': np.float64(-0.045082628434283095), 'Nlen_freq': np.float64(-0.08965770840684999), 'Vlen_freq': np.float64(0.1014327148711638)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4587359242577948), 'Macro_class': np.float64(0.16955595967348097), 'Fam_class': np.float64(-0.049193872126034946), 'Nlen_freq': np.float64(-0.09766072855360526), 'Vlen_freq': np.float64(0.10825566002041272)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.449113004068729), 'Macro_class': np.float64(0.14688409858336846), 'Fam_class': np.float64(-0.03856823063612457), 'Nlen_freq': np.float64(-0.07693410846833972), 'Vlen_freq': np.float64(0.08713697129752625)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423865178459903), 'Macro_class': np.float64(0.14742781941566868), 'Fam_class': np.float64(-0.04220551669299832), 'Nlen_freq': np.float64(-0.08408780951079178), 'Vlen_freq': np.float64(0.09331308004442623)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.17024904236382), 'Macro_class': np.float64(2.1574938416648703), 'Fam_class': np.float64(0.1487508414401298), 'Nlen_freq': np.float64(0.5918857045818261), 'Vlen_freq': np.float64(0.7592851766905914)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.570583117190072), 'Macro_class': np.float64(2.1734961937659016), 'Fam_class': np.float64(0.17813056393229595), 'Nlen_freq': np.float64(0.7070759708323205), 'Vlen_freq': np.float64(0.8707330907377497)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.007671217755954474</v>
+        <v>0.008866521762677437</v>
       </c>
       <c r="V5" t="n">
-        <v>9.835913388709884</v>
+        <v>11.30828958862227</v>
       </c>
       <c r="W5" t="n">
-        <v>5.631105420961853e-05</v>
+        <v>1.31306658993433e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_05_All_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2216711997682284</v>
+        <v>0.2215000730459347</v>
       </c>
       <c r="H2" t="n">
-        <v>534.5772144639448</v>
+        <v>534.0471112616439</v>
       </c>
       <c r="I2" t="n">
-        <v>2.805806715175607e-104</v>
+        <v>3.450072936797282e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.7278626313512</v>
+        <v>210.7741941668376</v>
       </c>
       <c r="K2" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>60.01615014140037</v>
+        <v>59.96981860591393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122684404002936</v>
+        <v>0.112293124223142</v>
       </c>
       <c r="N2" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
+          <t>{'const': 0.5562505171853904, 'N1ratio-ArgsPreds': -2.142785220917257}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
+          <t>{'const': 2.611073940529163e-166, 'N1ratio-ArgsPreds': 3.45007293679726e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47063794263311826}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311876)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311887)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.150007304593487)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2561305929104448</v>
+        <v>0.2559891611162162</v>
       </c>
       <c r="H3" t="n">
-        <v>322.9740245535776</v>
+        <v>322.7343213000123</v>
       </c>
       <c r="I3" t="n">
-        <v>2.910065023966609e-121</v>
+        <v>3.478149128954077e-121</v>
       </c>
       <c r="J3" t="n">
-        <v>201.3981882543137</v>
+        <v>201.4364800658168</v>
       </c>
       <c r="K3" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>34.67291225921895</v>
+        <v>34.65376635346739</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1073551110097621</v>
+        <v>0.1073755224231433</v>
       </c>
       <c r="N3" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.468074736893736, 'N1ratio-ArgsPreds': -2.1541524464711896, 'Macro_class': 0.03906670331136904}</t>
+          <t>{'const': 0.46759713933343233, 'N1ratio-ArgsPreds': -2.1505927061558614, 'Macro_class': 0.039083594067886765}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.6529452894676226e-104, 'N1ratio-ArgsPreds': 4.686242165715662e-109, 'Macro_class': 3.092084722918587e-20}</t>
+          <t>{'const': 2.057462797080746e-104, 'N1ratio-ArgsPreds': 5.60282708154891e-109, 'Macro_class': 3.006110011386466e-20}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4725017184539223, 'Macro_class': 0.18564003418732464}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4723527662906486, 'Macro_class': 0.18572029692647635}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48044962994406476), 'Macro_class': np.float64(0.21041285155911574)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48029741314299507), 'Macro_class': np.float64(0.2104803550006107)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4724823232149074), 'Macro_class': np.float64(0.18563241403972688)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723326306283815), 'Macro_class': np.float64(0.18571237995966106)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.323954575055623), 'Macro_class': np.float64(3.445939314221659)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.309811395632707), 'Macro_class': np.float64(3.4489088070281517)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.03445939314221647</v>
+        <v>0.0344890880702815</v>
       </c>
       <c r="V3" t="n">
-        <v>86.9047993084293</v>
+        <v>86.96315408108541</v>
       </c>
       <c r="W3" t="n">
-        <v>3.092084722918151e-20</v>
+        <v>3.00611001138544e-20</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2568493439592349</v>
+        <v>0.2567052339018109</v>
       </c>
       <c r="H4" t="n">
-        <v>216.0138575800651</v>
+        <v>215.8508017362221</v>
       </c>
       <c r="I4" t="n">
-        <v>2.391569004212337e-120</v>
+        <v>2.867528165101628e-120</v>
       </c>
       <c r="J4" t="n">
-        <v>201.2035907111796</v>
+        <v>201.2426076464075</v>
       </c>
       <c r="K4" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>23.18014068719065</v>
+        <v>23.16713504211468</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1073085817126291</v>
+        <v>0.1073293907447507</v>
       </c>
       <c r="N4" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4759888597113042, 'N1ratio-ArgsPreds': -2.128302572359495, 'Macro_class': 0.039635394293468545, 'Fam_class': -0.00025296341176478084}</t>
+          <t>{'const': 0.4754972936617287, 'N1ratio-ArgsPreds': -2.124803239354886, 'Macro_class': 0.03965103062451348, 'Fam_class': -0.00025250101394355077}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 2.6617230041474045e-100, 'N1ratio-ArgsPreds': 7.408631313802145e-103, 'Macro_class': 1.369513523252418e-20, 'Fam_class': 0.1782590179604581}</t>
+          <t>{'const': 3.378365265996894e-100, 'N1ratio-ArgsPreds': 8.888602376167719e-103, 'Macro_class': 1.3348856395966246e-20, 'Fam_class': 0.17911157189957144}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.46683168801591796, 'Macro_class': 0.18834238182381569, 'Fam_class': -0.027540527164735602}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46668840876272966, 'Macro_class': 0.18841668369174164, 'Fam_class': -0.027490185181807486}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4681480710880722), 'Macro_class': np.float64(0.2124084751565065), 'Fam_class': np.float64(-0.031084286040385028)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46798632275229957), 'Macro_class': np.float64(0.2124691981309034), 'Fam_class': np.float64(-0.031023368613961395)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45671089532940834), 'Macro_class': np.float64(0.18738519505749102), 'Fam_class': np.float64(-0.02680953279693525)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45655309861524346), 'Macro_class': np.float64(0.18745946987130344), 'Fam_class': np.float64(-0.02675953634864669)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.858484191258977), 'Macro_class': np.float64(3.511321132673396), 'Fam_class': np.float64(0.07187510487899469)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.844073185518024), 'Macro_class': np.float64(3.514105284443012), 'Fam_class': np.float64(0.07160727855945433)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.000718751048790045</v>
+        <v>0.0007160727855947124</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8134387765479</v>
+        <v>1.806331127606412</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1782590179603268</v>
+        <v>0.1791115718996747</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2657158657219123</v>
+        <v>0.2655869534128205</v>
       </c>
       <c r="H5" t="n">
-        <v>135.556739758906</v>
+        <v>135.4671913996732</v>
       </c>
       <c r="I5" t="n">
-        <v>7.158313357665104e-123</v>
+        <v>8.431280695247893e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>198.8030330298154</v>
+        <v>198.8379352656747</v>
       </c>
       <c r="K5" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L5" t="n">
-        <v>14.38819594858723</v>
+        <v>14.38121550141537</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1061415018845784</v>
+        <v>0.106160136287066</v>
       </c>
       <c r="N5" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4966621923199189, 'N1ratio-ArgsPreds': -2.079498707297034, 'Macro_class': 0.0335176877291935, 'Fam_class': -0.0004085471162188468, 'Nlen_freq': -0.45832254757103325, 'Vlen_freq': 0.5661226375859589}</t>
+          <t>{'const': 0.496527669313143, 'N1ratio-ArgsPreds': -2.076017194287994, 'Macro_class': 0.033540915032584016, 'Fam_class': -0.0004076623078639546, 'Nlen_freq': -0.4654514735555304, 'Vlen_freq': 0.5663991687897232}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.2789872833284822e-55, 'N1ratio-ArgsPreds': 3.199367485890837e-98, 'Macro_class': 1.4609515341634866e-13, 'Fam_class': 0.033169445271857965, 'Nlen_freq': 2.2739211578145297e-05, 'Vlen_freq': 2.623427328964937e-06}</t>
+          <t>{'const': 1.2627084477669889e-55, 'N1ratio-ArgsPreds': 3.95998127234126e-98, 'Macro_class': 1.4135893769776479e-13, 'Fam_class': 0.033576063608081554, 'Nlen_freq': 2.1592767582157648e-05, 'Vlen_freq': 2.6079550805940237e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.456126823489277, 'Macro_class': 0.15927181380868616, 'Fam_class': -0.044479171409823874, 'Nlen_freq': -0.15327235179880677, 'Vlen_freq': 0.1803240571907867}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4559731193089131, 'Macro_class': 0.15938218701732693, 'Fam_class': -0.04438284092327844, 'Nlen_freq': -0.1537549217111747, 'Vlen_freq': 0.18044583122953328}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4587359242577948), 'Macro_class': np.float64(0.16955595967348097), 'Fam_class': np.float64(-0.049193872126034946), 'Nlen_freq': np.float64(-0.09766072855360526), 'Vlen_freq': np.float64(0.10825566002041272)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4585402540022395), 'Macro_class': np.float64(0.16965499314907867), 'Fam_class': np.float64(-0.049080845291872344), 'Nlen_freq': np.float64(-0.09792704689769491), 'Vlen_freq': np.float64(0.10828333547990755)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423865178459903), 'Macro_class': np.float64(0.14742781941566868), 'Fam_class': np.float64(-0.04220551669299832), 'Nlen_freq': np.float64(-0.08408780951079178), 'Vlen_freq': np.float64(0.09331308004442623)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4421863799311869), 'Macro_class': np.float64(0.1475294280983914), 'Fam_class': np.float64(-0.04211200787694005), 'Nlen_freq': np.float64(-0.08432673336699999), 'Vlen_freq': np.float64(0.09334541131002518)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.570583117190072), 'Macro_class': np.float64(2.1734961937659016), 'Fam_class': np.float64(0.17813056393229595), 'Nlen_freq': np.float64(0.7070759708323205), 'Vlen_freq': np.float64(0.8707330907377497)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.552879459664798), 'Macro_class': np.float64(2.176493215503844), 'Fam_class': np.float64(0.17734212074274608), 'Nlen_freq': np.float64(0.7110997960349109), 'Vlen_freq': np.float64(0.8713365812637776)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.008866521762677437</v>
+        <v>0.008881719511009578</v>
       </c>
       <c r="V5" t="n">
-        <v>11.30828958862227</v>
+        <v>11.32568431445083</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31306658993433e-05</v>
+        <v>1.290691702371076e-05</v>
       </c>
     </row>
   </sheetData>
